--- a/docs/field/ArdaLink_Mom_Test_Tracker.xlsx
+++ b/docs/field/ArdaLink_Mom_Test_Tracker.xlsx
@@ -762,7 +762,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R22"/>
+  <dimension ref="A1:X26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -770,19 +770,25 @@
     <col width="34" customWidth="1" min="3" max="3"/>
     <col width="34" customWidth="1" min="4" max="4"/>
     <col width="4" customWidth="1" min="5" max="5"/>
-    <col width="5" customWidth="1" min="6" max="6"/>
-    <col width="5" customWidth="1" min="7" max="7"/>
-    <col width="5" customWidth="1" min="8" max="8"/>
-    <col width="5" customWidth="1" min="9" max="9"/>
-    <col width="5" customWidth="1" min="10" max="10"/>
-    <col width="5" customWidth="1" min="11" max="11"/>
-    <col width="5" customWidth="1" min="12" max="12"/>
-    <col width="5" customWidth="1" min="13" max="13"/>
-    <col width="5" customWidth="1" min="14" max="14"/>
-    <col width="5" customWidth="1" min="15" max="15"/>
-    <col width="8" customWidth="1" min="16" max="16"/>
-    <col width="8" customWidth="1" min="17" max="17"/>
-    <col width="15" customWidth="1" min="18" max="18"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="4" customWidth="1" min="7" max="7"/>
+    <col width="4" customWidth="1" min="8" max="8"/>
+    <col width="4" customWidth="1" min="9" max="9"/>
+    <col width="4" customWidth="1" min="10" max="10"/>
+    <col width="4" customWidth="1" min="11" max="11"/>
+    <col width="4" customWidth="1" min="12" max="12"/>
+    <col width="4" customWidth="1" min="13" max="13"/>
+    <col width="4" customWidth="1" min="14" max="14"/>
+    <col width="4" customWidth="1" min="15" max="15"/>
+    <col width="4" customWidth="1" min="16" max="16"/>
+    <col width="4" customWidth="1" min="17" max="17"/>
+    <col width="4" customWidth="1" min="18" max="18"/>
+    <col width="4" customWidth="1" min="19" max="19"/>
+    <col width="4" customWidth="1" min="20" max="20"/>
+    <col width="4" customWidth="1" min="21" max="21"/>
+    <col width="8" customWidth="1" min="22" max="22"/>
+    <col width="8" customWidth="1" min="23" max="23"/>
+    <col width="15" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -813,65 +819,95 @@
       </c>
       <c r="F1" s="3" t="inlineStr">
         <is>
+          <t>How tested</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
           <t>I01</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>I02</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>I03</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>I04</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="K1" s="3" t="inlineStr">
         <is>
           <t>I05</t>
         </is>
       </c>
-      <c r="K1" s="3" t="inlineStr">
+      <c r="L1" s="3" t="inlineStr">
         <is>
           <t>I06</t>
         </is>
       </c>
-      <c r="L1" s="3" t="inlineStr">
+      <c r="M1" s="3" t="inlineStr">
         <is>
           <t>I07</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
+      <c r="N1" s="3" t="inlineStr">
         <is>
           <t>I08</t>
         </is>
       </c>
-      <c r="N1" s="3" t="inlineStr">
+      <c r="O1" s="3" t="inlineStr">
         <is>
           <t>I09</t>
         </is>
       </c>
-      <c r="O1" s="3" t="inlineStr">
+      <c r="P1" s="3" t="inlineStr">
         <is>
           <t>I10</t>
         </is>
       </c>
-      <c r="P1" s="3" t="inlineStr">
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>I11</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>I12</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>I13</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
+        <is>
+          <t>I14</t>
+        </is>
+      </c>
+      <c r="U1" s="3" t="inlineStr">
+        <is>
+          <t>I15</t>
+        </is>
+      </c>
+      <c r="V1" s="3" t="inlineStr">
         <is>
           <t>Y count</t>
         </is>
       </c>
-      <c r="Q1" s="3" t="inlineStr">
+      <c r="W1" s="3" t="inlineStr">
         <is>
           <t>N count</t>
         </is>
       </c>
-      <c r="R1" s="3" t="inlineStr">
+      <c r="X1" s="3" t="inlineStr">
         <is>
           <t>Verdict</t>
         </is>
@@ -901,7 +937,11 @@
       <c r="E2" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="F2" s="5" t="n"/>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>B4-B9, C10-C15, D16-D21</t>
+        </is>
+      </c>
       <c r="G2" s="5" t="n"/>
       <c r="H2" s="5" t="n"/>
       <c r="I2" s="5" t="n"/>
@@ -911,16 +951,21 @@
       <c r="M2" s="5" t="n"/>
       <c r="N2" s="5" t="n"/>
       <c r="O2" s="5" t="n"/>
-      <c r="P2" s="5">
-        <f>COUNTIF(F2:O2,"Y")</f>
-        <v/>
-      </c>
-      <c r="Q2" s="5">
-        <f>COUNTIF(F2:O2,"N")</f>
-        <v/>
-      </c>
-      <c r="R2" s="5">
-        <f>IF(P2+Q2=0,"",IF(P2&gt;=E2,"SUPPORTED",IF(Q2&gt;=11-E2,"CONTRADICTED","UNKNOWN")))</f>
+      <c r="P2" s="5" t="n"/>
+      <c r="Q2" s="5" t="n"/>
+      <c r="R2" s="5" t="n"/>
+      <c r="S2" s="5" t="n"/>
+      <c r="T2" s="5" t="n"/>
+      <c r="U2" s="5">
+        <f>COUNTIF(F2:T2,"Y")</f>
+        <v/>
+      </c>
+      <c r="V2" s="5">
+        <f>COUNTIF(F2:T2,"N")</f>
+        <v/>
+      </c>
+      <c r="W2" s="5">
+        <f>IF(U2+V2=0,"",IF(U2&gt;=E2,"SUPPORTED",IF(V2&gt;=16-E2,"CONTRADICTED","UNKNOWN")))</f>
         <v/>
       </c>
     </row>
@@ -948,7 +993,11 @@
       <c r="E3" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="F3" s="5" t="n"/>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>C11-C12, E23-E26, H38</t>
+        </is>
+      </c>
       <c r="G3" s="5" t="n"/>
       <c r="H3" s="5" t="n"/>
       <c r="I3" s="5" t="n"/>
@@ -958,16 +1007,21 @@
       <c r="M3" s="5" t="n"/>
       <c r="N3" s="5" t="n"/>
       <c r="O3" s="5" t="n"/>
-      <c r="P3" s="5">
-        <f>COUNTIF(F3:O3,"Y")</f>
-        <v/>
-      </c>
-      <c r="Q3" s="5">
-        <f>COUNTIF(F3:O3,"N")</f>
-        <v/>
-      </c>
-      <c r="R3" s="5">
-        <f>IF(P3+Q3=0,"",IF(P3&gt;=E3,"SUPPORTED",IF(Q3&gt;=11-E3,"CONTRADICTED","UNKNOWN")))</f>
+      <c r="P3" s="5" t="n"/>
+      <c r="Q3" s="5" t="n"/>
+      <c r="R3" s="5" t="n"/>
+      <c r="S3" s="5" t="n"/>
+      <c r="T3" s="5" t="n"/>
+      <c r="U3" s="5">
+        <f>COUNTIF(F3:T3,"Y")</f>
+        <v/>
+      </c>
+      <c r="V3" s="5">
+        <f>COUNTIF(F3:T3,"N")</f>
+        <v/>
+      </c>
+      <c r="W3" s="5">
+        <f>IF(U3+V3=0,"",IF(U3&gt;=E3,"SUPPORTED",IF(V3&gt;=16-E3,"CONTRADICTED","UNKNOWN")))</f>
         <v/>
       </c>
     </row>
@@ -995,7 +1049,11 @@
       <c r="E4" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="F4" s="5" t="n"/>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>D19, H37, K51</t>
+        </is>
+      </c>
       <c r="G4" s="5" t="n"/>
       <c r="H4" s="5" t="n"/>
       <c r="I4" s="5" t="n"/>
@@ -1005,16 +1063,21 @@
       <c r="M4" s="5" t="n"/>
       <c r="N4" s="5" t="n"/>
       <c r="O4" s="5" t="n"/>
-      <c r="P4" s="5">
-        <f>COUNTIF(F4:O4,"Y")</f>
-        <v/>
-      </c>
-      <c r="Q4" s="5">
-        <f>COUNTIF(F4:O4,"N")</f>
-        <v/>
-      </c>
-      <c r="R4" s="5">
-        <f>IF(P4+Q4=0,"",IF(P4&gt;=E4,"SUPPORTED",IF(Q4&gt;=11-E4,"CONTRADICTED","UNKNOWN")))</f>
+      <c r="P4" s="5" t="n"/>
+      <c r="Q4" s="5" t="n"/>
+      <c r="R4" s="5" t="n"/>
+      <c r="S4" s="5" t="n"/>
+      <c r="T4" s="5" t="n"/>
+      <c r="U4" s="5">
+        <f>COUNTIF(F4:T4,"Y")</f>
+        <v/>
+      </c>
+      <c r="V4" s="5">
+        <f>COUNTIF(F4:T4,"N")</f>
+        <v/>
+      </c>
+      <c r="W4" s="5">
+        <f>IF(U4+V4=0,"",IF(U4&gt;=E4,"SUPPORTED",IF(V4&gt;=16-E4,"CONTRADICTED","UNKNOWN")))</f>
         <v/>
       </c>
     </row>
@@ -1042,7 +1105,11 @@
       <c r="E5" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="F5" s="5" t="n"/>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>B4, C10, D16</t>
+        </is>
+      </c>
       <c r="G5" s="5" t="n"/>
       <c r="H5" s="5" t="n"/>
       <c r="I5" s="5" t="n"/>
@@ -1052,16 +1119,21 @@
       <c r="M5" s="5" t="n"/>
       <c r="N5" s="5" t="n"/>
       <c r="O5" s="5" t="n"/>
-      <c r="P5" s="5">
-        <f>COUNTIF(F5:O5,"Y")</f>
-        <v/>
-      </c>
-      <c r="Q5" s="5">
-        <f>COUNTIF(F5:O5,"N")</f>
-        <v/>
-      </c>
-      <c r="R5" s="5">
-        <f>IF(P5+Q5=0,"",IF(P5&gt;=E5,"SUPPORTED",IF(Q5&gt;=11-E5,"CONTRADICTED","UNKNOWN")))</f>
+      <c r="P5" s="5" t="n"/>
+      <c r="Q5" s="5" t="n"/>
+      <c r="R5" s="5" t="n"/>
+      <c r="S5" s="5" t="n"/>
+      <c r="T5" s="5" t="n"/>
+      <c r="U5" s="5">
+        <f>COUNTIF(F5:T5,"Y")</f>
+        <v/>
+      </c>
+      <c r="V5" s="5">
+        <f>COUNTIF(F5:T5,"N")</f>
+        <v/>
+      </c>
+      <c r="W5" s="5">
+        <f>IF(U5+V5=0,"",IF(U5&gt;=E5,"SUPPORTED",IF(V5&gt;=16-E5,"CONTRADICTED","UNKNOWN")))</f>
         <v/>
       </c>
     </row>
@@ -1089,7 +1161,11 @@
       <c r="E6" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="F6" s="5" t="n"/>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>T1, T3, G36</t>
+        </is>
+      </c>
       <c r="G6" s="5" t="n"/>
       <c r="H6" s="5" t="n"/>
       <c r="I6" s="5" t="n"/>
@@ -1099,16 +1175,21 @@
       <c r="M6" s="5" t="n"/>
       <c r="N6" s="5" t="n"/>
       <c r="O6" s="5" t="n"/>
-      <c r="P6" s="5">
-        <f>COUNTIF(F6:O6,"Y")</f>
-        <v/>
-      </c>
-      <c r="Q6" s="5">
-        <f>COUNTIF(F6:O6,"N")</f>
-        <v/>
-      </c>
-      <c r="R6" s="5">
-        <f>IF(P6+Q6=0,"",IF(P6&gt;=E6,"SUPPORTED",IF(Q6&gt;=11-E6,"CONTRADICTED","UNKNOWN")))</f>
+      <c r="P6" s="5" t="n"/>
+      <c r="Q6" s="5" t="n"/>
+      <c r="R6" s="5" t="n"/>
+      <c r="S6" s="5" t="n"/>
+      <c r="T6" s="5" t="n"/>
+      <c r="U6" s="5">
+        <f>COUNTIF(F6:T6,"Y")</f>
+        <v/>
+      </c>
+      <c r="V6" s="5">
+        <f>COUNTIF(F6:T6,"N")</f>
+        <v/>
+      </c>
+      <c r="W6" s="5">
+        <f>IF(U6+V6=0,"",IF(U6&gt;=E6,"SUPPORTED",IF(V6&gt;=16-E6,"CONTRADICTED","UNKNOWN")))</f>
         <v/>
       </c>
     </row>
@@ -1136,7 +1217,11 @@
       <c r="E7" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="F7" s="5" t="n"/>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>T3, M57</t>
+        </is>
+      </c>
       <c r="G7" s="5" t="n"/>
       <c r="H7" s="5" t="n"/>
       <c r="I7" s="5" t="n"/>
@@ -1146,16 +1231,21 @@
       <c r="M7" s="5" t="n"/>
       <c r="N7" s="5" t="n"/>
       <c r="O7" s="5" t="n"/>
-      <c r="P7" s="5">
-        <f>COUNTIF(F7:O7,"Y")</f>
-        <v/>
-      </c>
-      <c r="Q7" s="5">
-        <f>COUNTIF(F7:O7,"N")</f>
-        <v/>
-      </c>
-      <c r="R7" s="5">
-        <f>IF(P7+Q7=0,"",IF(P7&gt;=E7,"SUPPORTED",IF(Q7&gt;=11-E7,"CONTRADICTED","UNKNOWN")))</f>
+      <c r="P7" s="5" t="n"/>
+      <c r="Q7" s="5" t="n"/>
+      <c r="R7" s="5" t="n"/>
+      <c r="S7" s="5" t="n"/>
+      <c r="T7" s="5" t="n"/>
+      <c r="U7" s="5">
+        <f>COUNTIF(F7:T7,"Y")</f>
+        <v/>
+      </c>
+      <c r="V7" s="5">
+        <f>COUNTIF(F7:T7,"N")</f>
+        <v/>
+      </c>
+      <c r="W7" s="5">
+        <f>IF(U7+V7=0,"",IF(U7&gt;=E7,"SUPPORTED",IF(V7&gt;=16-E7,"CONTRADICTED","UNKNOWN")))</f>
         <v/>
       </c>
     </row>
@@ -1183,7 +1273,11 @@
       <c r="E8" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="F8" s="5" t="n"/>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>T4, G35</t>
+        </is>
+      </c>
       <c r="G8" s="5" t="n"/>
       <c r="H8" s="5" t="n"/>
       <c r="I8" s="5" t="n"/>
@@ -1193,16 +1287,21 @@
       <c r="M8" s="5" t="n"/>
       <c r="N8" s="5" t="n"/>
       <c r="O8" s="5" t="n"/>
-      <c r="P8" s="5">
-        <f>COUNTIF(F8:O8,"Y")</f>
-        <v/>
-      </c>
-      <c r="Q8" s="5">
-        <f>COUNTIF(F8:O8,"N")</f>
-        <v/>
-      </c>
-      <c r="R8" s="5">
-        <f>IF(P8+Q8=0,"",IF(P8&gt;=E8,"SUPPORTED",IF(Q8&gt;=11-E8,"CONTRADICTED","UNKNOWN")))</f>
+      <c r="P8" s="5" t="n"/>
+      <c r="Q8" s="5" t="n"/>
+      <c r="R8" s="5" t="n"/>
+      <c r="S8" s="5" t="n"/>
+      <c r="T8" s="5" t="n"/>
+      <c r="U8" s="5">
+        <f>COUNTIF(F8:T8,"Y")</f>
+        <v/>
+      </c>
+      <c r="V8" s="5">
+        <f>COUNTIF(F8:T8,"N")</f>
+        <v/>
+      </c>
+      <c r="W8" s="5">
+        <f>IF(U8+V8=0,"",IF(U8&gt;=E8,"SUPPORTED",IF(V8&gt;=16-E8,"CONTRADICTED","UNKNOWN")))</f>
         <v/>
       </c>
     </row>
@@ -1230,7 +1329,11 @@
       <c r="E9" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="F9" s="5" t="n"/>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
       <c r="G9" s="5" t="n"/>
       <c r="H9" s="5" t="n"/>
       <c r="I9" s="5" t="n"/>
@@ -1240,16 +1343,21 @@
       <c r="M9" s="5" t="n"/>
       <c r="N9" s="5" t="n"/>
       <c r="O9" s="5" t="n"/>
-      <c r="P9" s="5">
-        <f>COUNTIF(F9:O9,"Y")</f>
-        <v/>
-      </c>
-      <c r="Q9" s="5">
-        <f>COUNTIF(F9:O9,"N")</f>
-        <v/>
-      </c>
-      <c r="R9" s="5">
-        <f>IF(P9+Q9=0,"",IF(P9&gt;=E9,"SUPPORTED",IF(Q9&gt;=11-E9,"CONTRADICTED","UNKNOWN")))</f>
+      <c r="P9" s="5" t="n"/>
+      <c r="Q9" s="5" t="n"/>
+      <c r="R9" s="5" t="n"/>
+      <c r="S9" s="5" t="n"/>
+      <c r="T9" s="5" t="n"/>
+      <c r="U9" s="5">
+        <f>COUNTIF(F9:T9,"Y")</f>
+        <v/>
+      </c>
+      <c r="V9" s="5">
+        <f>COUNTIF(F9:T9,"N")</f>
+        <v/>
+      </c>
+      <c r="W9" s="5">
+        <f>IF(U9+V9=0,"",IF(U9&gt;=E9,"SUPPORTED",IF(V9&gt;=16-E9,"CONTRADICTED","UNKNOWN")))</f>
         <v/>
       </c>
     </row>
@@ -1277,7 +1385,11 @@
       <c r="E10" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="F10" s="5" t="n"/>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>T6</t>
+        </is>
+      </c>
       <c r="G10" s="5" t="n"/>
       <c r="H10" s="5" t="n"/>
       <c r="I10" s="5" t="n"/>
@@ -1287,16 +1399,21 @@
       <c r="M10" s="5" t="n"/>
       <c r="N10" s="5" t="n"/>
       <c r="O10" s="5" t="n"/>
-      <c r="P10" s="5">
-        <f>COUNTIF(F10:O10,"Y")</f>
-        <v/>
-      </c>
-      <c r="Q10" s="5">
-        <f>COUNTIF(F10:O10,"N")</f>
-        <v/>
-      </c>
-      <c r="R10" s="5">
-        <f>IF(P10+Q10=0,"",IF(P10&gt;=E10,"SUPPORTED",IF(Q10&gt;=11-E10,"CONTRADICTED","UNKNOWN")))</f>
+      <c r="P10" s="5" t="n"/>
+      <c r="Q10" s="5" t="n"/>
+      <c r="R10" s="5" t="n"/>
+      <c r="S10" s="5" t="n"/>
+      <c r="T10" s="5" t="n"/>
+      <c r="U10" s="5">
+        <f>COUNTIF(F10:T10,"Y")</f>
+        <v/>
+      </c>
+      <c r="V10" s="5">
+        <f>COUNTIF(F10:T10,"N")</f>
+        <v/>
+      </c>
+      <c r="W10" s="5">
+        <f>IF(U10+V10=0,"",IF(U10&gt;=E10,"SUPPORTED",IF(V10&gt;=16-E10,"CONTRADICTED","UNKNOWN")))</f>
         <v/>
       </c>
     </row>
@@ -1324,7 +1441,11 @@
       <c r="E11" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="F11" s="5" t="n"/>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>T7, I42</t>
+        </is>
+      </c>
       <c r="G11" s="5" t="n"/>
       <c r="H11" s="5" t="n"/>
       <c r="I11" s="5" t="n"/>
@@ -1334,16 +1455,21 @@
       <c r="M11" s="5" t="n"/>
       <c r="N11" s="5" t="n"/>
       <c r="O11" s="5" t="n"/>
-      <c r="P11" s="5">
-        <f>COUNTIF(F11:O11,"Y")</f>
-        <v/>
-      </c>
-      <c r="Q11" s="5">
-        <f>COUNTIF(F11:O11,"N")</f>
-        <v/>
-      </c>
-      <c r="R11" s="5">
-        <f>IF(P11+Q11=0,"",IF(P11&gt;=E11,"SUPPORTED",IF(Q11&gt;=11-E11,"CONTRADICTED","UNKNOWN")))</f>
+      <c r="P11" s="5" t="n"/>
+      <c r="Q11" s="5" t="n"/>
+      <c r="R11" s="5" t="n"/>
+      <c r="S11" s="5" t="n"/>
+      <c r="T11" s="5" t="n"/>
+      <c r="U11" s="5">
+        <f>COUNTIF(F11:T11,"Y")</f>
+        <v/>
+      </c>
+      <c r="V11" s="5">
+        <f>COUNTIF(F11:T11,"N")</f>
+        <v/>
+      </c>
+      <c r="W11" s="5">
+        <f>IF(U11+V11=0,"",IF(U11&gt;=E11,"SUPPORTED",IF(V11&gt;=16-E11,"CONTRADICTED","UNKNOWN")))</f>
         <v/>
       </c>
     </row>
@@ -1371,7 +1497,11 @@
       <c r="E12" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="F12" s="5" t="n"/>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>T5</t>
+        </is>
+      </c>
       <c r="G12" s="5" t="n"/>
       <c r="H12" s="5" t="n"/>
       <c r="I12" s="5" t="n"/>
@@ -1381,44 +1511,53 @@
       <c r="M12" s="5" t="n"/>
       <c r="N12" s="5" t="n"/>
       <c r="O12" s="5" t="n"/>
-      <c r="P12" s="5">
-        <f>COUNTIF(F12:O12,"Y")</f>
-        <v/>
-      </c>
-      <c r="Q12" s="5">
-        <f>COUNTIF(F12:O12,"N")</f>
-        <v/>
-      </c>
-      <c r="R12" s="5">
-        <f>IF(P12+Q12=0,"",IF(P12&gt;=E12,"SUPPORTED",IF(Q12&gt;=11-E12,"CONTRADICTED","UNKNOWN")))</f>
+      <c r="P12" s="5" t="n"/>
+      <c r="Q12" s="5" t="n"/>
+      <c r="R12" s="5" t="n"/>
+      <c r="S12" s="5" t="n"/>
+      <c r="T12" s="5" t="n"/>
+      <c r="U12" s="5">
+        <f>COUNTIF(F12:T12,"Y")</f>
+        <v/>
+      </c>
+      <c r="V12" s="5">
+        <f>COUNTIF(F12:T12,"N")</f>
+        <v/>
+      </c>
+      <c r="W12" s="5">
+        <f>IF(U12+V12=0,"",IF(U12&gt;=E12,"SUPPORTED",IF(V12&gt;=16-E12,"CONTRADICTED","UNKNOWN")))</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>V1</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Somebody already pays for this kind of information</t>
+          <t>He already passes information on, or will</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>A named budget line or a real past payment</t>
+          <t>&gt;=6/10 describe a specific time they passed on water or pest news</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Nobody pays</t>
+          <t>Nobody has ever reported anything to anyone</t>
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="F13" s="5" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>L52-L55</t>
+        </is>
+      </c>
       <c r="G13" s="5" t="n"/>
       <c r="H13" s="5" t="n"/>
       <c r="I13" s="5" t="n"/>
@@ -1428,44 +1567,53 @@
       <c r="M13" s="5" t="n"/>
       <c r="N13" s="5" t="n"/>
       <c r="O13" s="5" t="n"/>
-      <c r="P13" s="5">
-        <f>COUNTIF(F13:O13,"Y")</f>
-        <v/>
-      </c>
-      <c r="Q13" s="5">
-        <f>COUNTIF(F13:O13,"N")</f>
-        <v/>
-      </c>
-      <c r="R13" s="5">
-        <f>IF(P13+Q13=0,"",IF(P13&gt;=E13,"SUPPORTED",IF(Q13&gt;=11-E13,"CONTRADICTED","UNKNOWN")))</f>
+      <c r="P13" s="5" t="n"/>
+      <c r="Q13" s="5" t="n"/>
+      <c r="R13" s="5" t="n"/>
+      <c r="S13" s="5" t="n"/>
+      <c r="T13" s="5" t="n"/>
+      <c r="U13" s="5">
+        <f>COUNTIF(F13:T13,"Y")</f>
+        <v/>
+      </c>
+      <c r="V13" s="5">
+        <f>COUNTIF(F13:T13,"N")</f>
+        <v/>
+      </c>
+      <c r="W13" s="5">
+        <f>IF(U13+V13=0,"",IF(U13&gt;=E13,"SUPPORTED",IF(V13&gt;=16-E13,"CONTRADICTED","UNKNOWN")))</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>V2</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>The herder pays something, however small</t>
+          <t>One tap is a price he will pay for the value he gets back</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>&gt;=4/10 pay monthly for phone or vet services</t>
+          <t>&gt;=6/10 complete a report unaided, or agree to a test</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>0/10 pay anything</t>
+          <t>Most refuse</t>
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="F14" s="5" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>T3, L53, M57</t>
+        </is>
+      </c>
       <c r="G14" s="5" t="n"/>
       <c r="H14" s="5" t="n"/>
       <c r="I14" s="5" t="n"/>
@@ -1475,44 +1623,53 @@
       <c r="M14" s="5" t="n"/>
       <c r="N14" s="5" t="n"/>
       <c r="O14" s="5" t="n"/>
-      <c r="P14" s="5">
-        <f>COUNTIF(F14:O14,"Y")</f>
-        <v/>
-      </c>
-      <c r="Q14" s="5">
-        <f>COUNTIF(F14:O14,"N")</f>
-        <v/>
-      </c>
-      <c r="R14" s="5">
-        <f>IF(P14+Q14=0,"",IF(P14&gt;=E14,"SUPPORTED",IF(Q14&gt;=11-E14,"CONTRADICTED","UNKNOWN")))</f>
+      <c r="P14" s="5" t="n"/>
+      <c r="Q14" s="5" t="n"/>
+      <c r="R14" s="5" t="n"/>
+      <c r="S14" s="5" t="n"/>
+      <c r="T14" s="5" t="n"/>
+      <c r="U14" s="5">
+        <f>COUNTIF(F14:T14,"Y")</f>
+        <v/>
+      </c>
+      <c r="V14" s="5">
+        <f>COUNTIF(F14:T14,"N")</f>
+        <v/>
+      </c>
+      <c r="W14" s="5">
+        <f>IF(U14+V14=0,"",IF(U14&gt;=E14,"SUPPORTED",IF(V14&gt;=16-E14,"CONTRADICTED","UNKNOWN")))</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>V3</t>
+          <t>S3</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>The chief, the agrovet and the water committee will carry it</t>
+          <t>His reports are good enough to sell</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>&gt;=3 credible distribution offers, with names</t>
+          <t>Place names, status and timing are what a buyer would accept</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Nobody carries it</t>
+          <t>Too coarse or too late</t>
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="F15" s="5" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>L54, T2, T3</t>
+        </is>
+      </c>
       <c r="G15" s="5" t="n"/>
       <c r="H15" s="5" t="n"/>
       <c r="I15" s="5" t="n"/>
@@ -1522,44 +1679,53 @@
       <c r="M15" s="5" t="n"/>
       <c r="N15" s="5" t="n"/>
       <c r="O15" s="5" t="n"/>
-      <c r="P15" s="5">
-        <f>COUNTIF(F15:O15,"Y")</f>
-        <v/>
-      </c>
-      <c r="Q15" s="5">
-        <f>COUNTIF(F15:O15,"N")</f>
-        <v/>
-      </c>
-      <c r="R15" s="5">
-        <f>IF(P15+Q15=0,"",IF(P15&gt;=E15,"SUPPORTED",IF(Q15&gt;=11-E15,"CONTRADICTED","UNKNOWN")))</f>
+      <c r="P15" s="5" t="n"/>
+      <c r="Q15" s="5" t="n"/>
+      <c r="R15" s="5" t="n"/>
+      <c r="S15" s="5" t="n"/>
+      <c r="T15" s="5" t="n"/>
+      <c r="U15" s="5">
+        <f>COUNTIF(F15:T15,"Y")</f>
+        <v/>
+      </c>
+      <c r="V15" s="5">
+        <f>COUNTIF(F15:T15,"N")</f>
+        <v/>
+      </c>
+      <c r="W15" s="5">
+        <f>IF(U15+V15=0,"",IF(U15&gt;=E15,"SUPPORTED",IF(V15&gt;=16-E15,"CONTRADICTED","UNKNOWN")))</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>V4</t>
+          <t>S4</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>No gatekeeper blocks it</t>
+          <t>He keeps contributing without being paid</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Nobody objects or claims ownership</t>
+          <t>He names a concrete gain and is still reporting two weeks later</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>A veto appears</t>
+          <t>One report, then silence</t>
         </is>
       </c>
       <c r="E16" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="F16" s="5" t="n"/>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>K48, K51, T4, the 2-week call</t>
+        </is>
+      </c>
       <c r="G16" s="5" t="n"/>
       <c r="H16" s="5" t="n"/>
       <c r="I16" s="5" t="n"/>
@@ -1569,44 +1735,53 @@
       <c r="M16" s="5" t="n"/>
       <c r="N16" s="5" t="n"/>
       <c r="O16" s="5" t="n"/>
-      <c r="P16" s="5">
-        <f>COUNTIF(F16:O16,"Y")</f>
-        <v/>
-      </c>
-      <c r="Q16" s="5">
-        <f>COUNTIF(F16:O16,"N")</f>
-        <v/>
-      </c>
-      <c r="R16" s="5">
-        <f>IF(P16+Q16=0,"",IF(P16&gt;=E16,"SUPPORTED",IF(Q16&gt;=11-E16,"CONTRADICTED","UNKNOWN")))</f>
+      <c r="P16" s="5" t="n"/>
+      <c r="Q16" s="5" t="n"/>
+      <c r="R16" s="5" t="n"/>
+      <c r="S16" s="5" t="n"/>
+      <c r="T16" s="5" t="n"/>
+      <c r="U16" s="5">
+        <f>COUNTIF(F16:T16,"Y")</f>
+        <v/>
+      </c>
+      <c r="V16" s="5">
+        <f>COUNTIF(F16:T16,"N")</f>
+        <v/>
+      </c>
+      <c r="W16" s="5">
+        <f>IF(U16+V16=0,"",IF(U16&gt;=E16,"SUPPORTED",IF(V16&gt;=16-E16,"CONTRADICTED","UNKNOWN")))</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>I1</t>
+          <t>V1</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Early information reaches the household, not only the herd owner</t>
+          <t>An institution already pays to collect this kind of data</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>Women and phone-sharers describe concrete household gains</t>
+          <t>A named buyer with a real current spend (fuel, staff, surveys, M&amp;E)</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>The beneficiary never sees the message</t>
+          <t>Nobody spends anything on it</t>
         </is>
       </c>
       <c r="E17" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="F17" s="5" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>informant C2, C5, J46</t>
+        </is>
+      </c>
       <c r="G17" s="5" t="n"/>
       <c r="H17" s="5" t="n"/>
       <c r="I17" s="5" t="n"/>
@@ -1616,44 +1791,53 @@
       <c r="M17" s="5" t="n"/>
       <c r="N17" s="5" t="n"/>
       <c r="O17" s="5" t="n"/>
-      <c r="P17" s="5">
-        <f>COUNTIF(F17:O17,"Y")</f>
-        <v/>
-      </c>
-      <c r="Q17" s="5">
-        <f>COUNTIF(F17:O17,"N")</f>
-        <v/>
-      </c>
-      <c r="R17" s="5">
-        <f>IF(P17+Q17=0,"",IF(P17&gt;=E17,"SUPPORTED",IF(Q17&gt;=11-E17,"CONTRADICTED","UNKNOWN")))</f>
+      <c r="P17" s="5" t="n"/>
+      <c r="Q17" s="5" t="n"/>
+      <c r="R17" s="5" t="n"/>
+      <c r="S17" s="5" t="n"/>
+      <c r="T17" s="5" t="n"/>
+      <c r="U17" s="5">
+        <f>COUNTIF(F17:T17,"Y")</f>
+        <v/>
+      </c>
+      <c r="V17" s="5">
+        <f>COUNTIF(F17:T17,"N")</f>
+        <v/>
+      </c>
+      <c r="W17" s="5">
+        <f>IF(U17+V17=0,"",IF(U17&gt;=E17,"SUPPORTED",IF(V17&gt;=16-E17,"CONTRADICTED","UNKNOWN")))</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>I2</t>
+          <t>V2</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>The change is fewer wasted walks, less milk drop, fewer dead animals</t>
+          <t>That spend is reachable: a budget line, an owner, a cycle</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Two or more describable in numbers</t>
+          <t>A line item, a named officer, a date when it is decided</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Only it feels useful</t>
+          <t>Only good intentions, no line</t>
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="F18" s="5" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>informant C2.4, C5.2, C5.4</t>
+        </is>
+      </c>
       <c r="G18" s="5" t="n"/>
       <c r="H18" s="5" t="n"/>
       <c r="I18" s="5" t="n"/>
@@ -1663,44 +1847,53 @@
       <c r="M18" s="5" t="n"/>
       <c r="N18" s="5" t="n"/>
       <c r="O18" s="5" t="n"/>
-      <c r="P18" s="5">
-        <f>COUNTIF(F18:O18,"Y")</f>
-        <v/>
-      </c>
-      <c r="Q18" s="5">
-        <f>COUNTIF(F18:O18,"N")</f>
-        <v/>
-      </c>
-      <c r="R18" s="5">
-        <f>IF(P18+Q18=0,"",IF(P18&gt;=E18,"SUPPORTED",IF(Q18&gt;=11-E18,"CONTRADICTED","UNKNOWN")))</f>
+      <c r="P18" s="5" t="n"/>
+      <c r="Q18" s="5" t="n"/>
+      <c r="R18" s="5" t="n"/>
+      <c r="S18" s="5" t="n"/>
+      <c r="T18" s="5" t="n"/>
+      <c r="U18" s="5">
+        <f>COUNTIF(F18:T18,"Y")</f>
+        <v/>
+      </c>
+      <c r="V18" s="5">
+        <f>COUNTIF(F18:T18,"N")</f>
+        <v/>
+      </c>
+      <c r="W18" s="5">
+        <f>IF(U18+V18=0,"",IF(U18&gt;=E18,"SUPPORTED",IF(V18&gt;=16-E18,"CONTRADICTED","UNKNOWN")))</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>V3</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>A pastoralist decides where to move, and is able to move</t>
+          <t>The chief, the agrovet and the water committee will carry it</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>&gt;=3 credible distribution offers, with names</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>The decision is collective, or animals are held by a relative</t>
+          <t>Nobody carries it</t>
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="F19" s="5" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>M58, M59, informants</t>
+        </is>
+      </c>
       <c r="G19" s="5" t="n"/>
       <c r="H19" s="5" t="n"/>
       <c r="I19" s="5" t="n"/>
@@ -1710,44 +1903,53 @@
       <c r="M19" s="5" t="n"/>
       <c r="N19" s="5" t="n"/>
       <c r="O19" s="5" t="n"/>
-      <c r="P19" s="5">
-        <f>COUNTIF(F19:O19,"Y")</f>
-        <v/>
-      </c>
-      <c r="Q19" s="5">
-        <f>COUNTIF(F19:O19,"N")</f>
-        <v/>
-      </c>
-      <c r="R19" s="5">
-        <f>IF(P19+Q19=0,"",IF(P19&gt;=E19,"SUPPORTED",IF(Q19&gt;=11-E19,"CONTRADICTED","UNKNOWN")))</f>
+      <c r="P19" s="5" t="n"/>
+      <c r="Q19" s="5" t="n"/>
+      <c r="R19" s="5" t="n"/>
+      <c r="S19" s="5" t="n"/>
+      <c r="T19" s="5" t="n"/>
+      <c r="U19" s="5">
+        <f>COUNTIF(F19:T19,"Y")</f>
+        <v/>
+      </c>
+      <c r="V19" s="5">
+        <f>COUNTIF(F19:T19,"N")</f>
+        <v/>
+      </c>
+      <c r="W19" s="5">
+        <f>IF(U19+V19=0,"",IF(U19&gt;=E19,"SUPPORTED",IF(V19&gt;=16-E19,"CONTRADICTED","UNKNOWN")))</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>V4</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>He wants advice from a phone more than his current sources</t>
+          <t>No gatekeeper blocks it</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Nobody objects or claims ownership</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>He trusts the chief or radio, and says a phone cannot be checked</t>
+          <t>A veto appears</t>
         </is>
       </c>
       <c r="E20" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="F20" s="5" t="n"/>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>informants, I44</t>
+        </is>
+      </c>
       <c r="G20" s="5" t="n"/>
       <c r="H20" s="5" t="n"/>
       <c r="I20" s="5" t="n"/>
@@ -1757,44 +1959,53 @@
       <c r="M20" s="5" t="n"/>
       <c r="N20" s="5" t="n"/>
       <c r="O20" s="5" t="n"/>
-      <c r="P20" s="5">
-        <f>COUNTIF(F20:O20,"Y")</f>
-        <v/>
-      </c>
-      <c r="Q20" s="5">
-        <f>COUNTIF(F20:O20,"N")</f>
-        <v/>
-      </c>
-      <c r="R20" s="5">
-        <f>IF(P20+Q20=0,"",IF(P20&gt;=E20,"SUPPORTED",IF(Q20&gt;=11-E20,"CONTRADICTED","UNKNOWN")))</f>
+      <c r="P20" s="5" t="n"/>
+      <c r="Q20" s="5" t="n"/>
+      <c r="R20" s="5" t="n"/>
+      <c r="S20" s="5" t="n"/>
+      <c r="T20" s="5" t="n"/>
+      <c r="U20" s="5">
+        <f>COUNTIF(F20:T20,"Y")</f>
+        <v/>
+      </c>
+      <c r="V20" s="5">
+        <f>COUNTIF(F20:T20,"N")</f>
+        <v/>
+      </c>
+      <c r="W20" s="5">
+        <f>IF(U20+V20=0,"",IF(U20&gt;=E20,"SUPPORTED",IF(V20&gt;=16-E20,"CONTRADICTED","UNKNOWN")))</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>A3</t>
+          <t>I1</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Our data is good enough at the decision moment</t>
+          <t>Early information reaches the household, not only the herd owner</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Women and phone-sharers describe concrete household gains</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>He corrects most of what we show him</t>
+          <t>The beneficiary never sees the message</t>
         </is>
       </c>
       <c r="E21" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="F21" s="5" t="n"/>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>K48-K51, G32</t>
+        </is>
+      </c>
       <c r="G21" s="5" t="n"/>
       <c r="H21" s="5" t="n"/>
       <c r="I21" s="5" t="n"/>
@@ -1804,44 +2015,53 @@
       <c r="M21" s="5" t="n"/>
       <c r="N21" s="5" t="n"/>
       <c r="O21" s="5" t="n"/>
-      <c r="P21" s="5">
-        <f>COUNTIF(F21:O21,"Y")</f>
-        <v/>
-      </c>
-      <c r="Q21" s="5">
-        <f>COUNTIF(F21:O21,"N")</f>
-        <v/>
-      </c>
-      <c r="R21" s="5">
-        <f>IF(P21+Q21=0,"",IF(P21&gt;=E21,"SUPPORTED",IF(Q21&gt;=11-E21,"CONTRADICTED","UNKNOWN")))</f>
+      <c r="P21" s="5" t="n"/>
+      <c r="Q21" s="5" t="n"/>
+      <c r="R21" s="5" t="n"/>
+      <c r="S21" s="5" t="n"/>
+      <c r="T21" s="5" t="n"/>
+      <c r="U21" s="5">
+        <f>COUNTIF(F21:T21,"Y")</f>
+        <v/>
+      </c>
+      <c r="V21" s="5">
+        <f>COUNTIF(F21:T21,"N")</f>
+        <v/>
+      </c>
+      <c r="W21" s="5">
+        <f>IF(U21+V21=0,"",IF(U21&gt;=E21,"SUPPORTED",IF(V21&gt;=16-E21,"CONTRADICTED","UNKNOWN")))</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>A4</t>
+          <t>I2</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>We can reach him without an NGO or the county</t>
+          <t>The change is fewer wasted walks, less milk drop, fewer dead animals</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Two or more describable in numbers</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Distribution needs a gatekeeper we do not have</t>
+          <t>Only it feels useful</t>
         </is>
       </c>
       <c r="E22" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="F22" s="5" t="n"/>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>C12, D19, K49</t>
+        </is>
+      </c>
       <c r="G22" s="5" t="n"/>
       <c r="H22" s="5" t="n"/>
       <c r="I22" s="5" t="n"/>
@@ -1851,22 +2071,251 @@
       <c r="M22" s="5" t="n"/>
       <c r="N22" s="5" t="n"/>
       <c r="O22" s="5" t="n"/>
-      <c r="P22" s="5">
-        <f>COUNTIF(F22:O22,"Y")</f>
-        <v/>
-      </c>
-      <c r="Q22" s="5">
-        <f>COUNTIF(F22:O22,"N")</f>
-        <v/>
-      </c>
-      <c r="R22" s="5">
-        <f>IF(P22+Q22=0,"",IF(P22&gt;=E22,"SUPPORTED",IF(Q22&gt;=11-E22,"CONTRADICTED","UNKNOWN")))</f>
+      <c r="P22" s="5" t="n"/>
+      <c r="Q22" s="5" t="n"/>
+      <c r="R22" s="5" t="n"/>
+      <c r="S22" s="5" t="n"/>
+      <c r="T22" s="5" t="n"/>
+      <c r="U22" s="5">
+        <f>COUNTIF(F22:T22,"Y")</f>
+        <v/>
+      </c>
+      <c r="V22" s="5">
+        <f>COUNTIF(F22:T22,"N")</f>
+        <v/>
+      </c>
+      <c r="W22" s="5">
+        <f>IF(U22+V22=0,"",IF(U22&gt;=E22,"SUPPORTED",IF(V22&gt;=16-E22,"CONTRADICTED","UNKNOWN")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>A pastoralist decides where to move, and is able to move</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>The decision is collective, or animals are held by a relative</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>B4-B9</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="n"/>
+      <c r="H23" s="5" t="n"/>
+      <c r="I23" s="5" t="n"/>
+      <c r="J23" s="5" t="n"/>
+      <c r="K23" s="5" t="n"/>
+      <c r="L23" s="5" t="n"/>
+      <c r="M23" s="5" t="n"/>
+      <c r="N23" s="5" t="n"/>
+      <c r="O23" s="5" t="n"/>
+      <c r="P23" s="5" t="n"/>
+      <c r="Q23" s="5" t="n"/>
+      <c r="R23" s="5" t="n"/>
+      <c r="S23" s="5" t="n"/>
+      <c r="T23" s="5" t="n"/>
+      <c r="U23" s="5">
+        <f>COUNTIF(F23:T23,"Y")</f>
+        <v/>
+      </c>
+      <c r="V23" s="5">
+        <f>COUNTIF(F23:T23,"N")</f>
+        <v/>
+      </c>
+      <c r="W23" s="5">
+        <f>IF(U23+V23=0,"",IF(U23&gt;=E23,"SUPPORTED",IF(V23&gt;=16-E23,"CONTRADICTED","UNKNOWN")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>He wants advice from a phone more than his current sources</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>He trusts the chief or radio, and says a phone cannot be checked</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>F27-F31, I43</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="n"/>
+      <c r="H24" s="5" t="n"/>
+      <c r="I24" s="5" t="n"/>
+      <c r="J24" s="5" t="n"/>
+      <c r="K24" s="5" t="n"/>
+      <c r="L24" s="5" t="n"/>
+      <c r="M24" s="5" t="n"/>
+      <c r="N24" s="5" t="n"/>
+      <c r="O24" s="5" t="n"/>
+      <c r="P24" s="5" t="n"/>
+      <c r="Q24" s="5" t="n"/>
+      <c r="R24" s="5" t="n"/>
+      <c r="S24" s="5" t="n"/>
+      <c r="T24" s="5" t="n"/>
+      <c r="U24" s="5">
+        <f>COUNTIF(F24:T24,"Y")</f>
+        <v/>
+      </c>
+      <c r="V24" s="5">
+        <f>COUNTIF(F24:T24,"N")</f>
+        <v/>
+      </c>
+      <c r="W24" s="5">
+        <f>IF(U24+V24=0,"",IF(U24&gt;=E24,"SUPPORTED",IF(V24&gt;=16-E24,"CONTRADICTED","UNKNOWN")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Our data is good enough at the decision moment</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>He corrects most of what we show him</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>T2, T5, T6</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="n"/>
+      <c r="H25" s="5" t="n"/>
+      <c r="I25" s="5" t="n"/>
+      <c r="J25" s="5" t="n"/>
+      <c r="K25" s="5" t="n"/>
+      <c r="L25" s="5" t="n"/>
+      <c r="M25" s="5" t="n"/>
+      <c r="N25" s="5" t="n"/>
+      <c r="O25" s="5" t="n"/>
+      <c r="P25" s="5" t="n"/>
+      <c r="Q25" s="5" t="n"/>
+      <c r="R25" s="5" t="n"/>
+      <c r="S25" s="5" t="n"/>
+      <c r="T25" s="5" t="n"/>
+      <c r="U25" s="5">
+        <f>COUNTIF(F25:T25,"Y")</f>
+        <v/>
+      </c>
+      <c r="V25" s="5">
+        <f>COUNTIF(F25:T25,"N")</f>
+        <v/>
+      </c>
+      <c r="W25" s="5">
+        <f>IF(U25+V25=0,"",IF(U25&gt;=E25,"SUPPORTED",IF(V25&gt;=16-E25,"CONTRADICTED","UNKNOWN")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>We can reach him without an NGO or the county</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>Distribution needs a gatekeeper we do not have</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>informants, M58</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="n"/>
+      <c r="H26" s="5" t="n"/>
+      <c r="I26" s="5" t="n"/>
+      <c r="J26" s="5" t="n"/>
+      <c r="K26" s="5" t="n"/>
+      <c r="L26" s="5" t="n"/>
+      <c r="M26" s="5" t="n"/>
+      <c r="N26" s="5" t="n"/>
+      <c r="O26" s="5" t="n"/>
+      <c r="P26" s="5" t="n"/>
+      <c r="Q26" s="5" t="n"/>
+      <c r="R26" s="5" t="n"/>
+      <c r="S26" s="5" t="n"/>
+      <c r="T26" s="5" t="n"/>
+      <c r="U26" s="5">
+        <f>COUNTIF(F26:T26,"Y")</f>
+        <v/>
+      </c>
+      <c r="V26" s="5">
+        <f>COUNTIF(F26:T26,"N")</f>
+        <v/>
+      </c>
+      <c r="W26" s="5">
+        <f>IF(U26+V26=0,"",IF(U26&gt;=E26,"SUPPORTED",IF(V26&gt;=16-E26,"CONTRADICTED","UNKNOWN")))</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="F2:O22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F2:T26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Y,N,?"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2236,7 +2685,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2280,12 +2729,12 @@
       </c>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Can pay?</t>
+          <t>Gives (data)</t>
         </is>
       </c>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Can block?</t>
+          <t>Pays?</t>
         </is>
       </c>
       <c r="H1" s="3" t="inlineStr">
@@ -2312,7 +2761,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Herder / owner — decision maker</t>
+          <t>Herder / owner — user, decision maker</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -2327,13 +2776,21 @@
           <t>Wasted walks, dead animals, milk drop</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>One-tap report from the point</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Never pays</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Young herder — daily with the animals</t>
+          <t>Young herder — user, daily with the animals</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -2348,8 +2805,16 @@
           <t>Hours, km, heat</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>The most reports, most often</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Never pays</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2369,8 +2834,16 @@
           <t>Walks to water, milk loss, sick shoats</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Queue and shoats observations</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Never pays</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2390,8 +2863,16 @@
           <t>Nutrition when herds fail</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Nothing — he is why the herder never pays</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Never pays</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2411,8 +2892,16 @@
           <t>Queue conflict, breakdowns</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Confirms repairs, validates reports</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>No (may hold a fund)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2432,92 +2921,161 @@
           <t>Wrong products bought, no follow-up</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Distribution; pest observations at the counter</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Maybe — footfall/stock data</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>County vet / livestock officer — content review</t>
+          <t>County livestock / water dept — BUYER</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Surveillance</t>
+          <t>Surveillance, service delivery, fewer outbreaks</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>No ground-level data</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
+          <t>Collecting ward ground truth by vehicle and phone</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Nothing (or it reviews our wording)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>YES — county budget line</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Chief / ward admin — distribution</t>
+          <t>NDMA ward officer — BUYER / data partner</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Order, service, being seen to help</t>
+          <t>Timely ward ground truth on water and pasture</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Nothing</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
+          <t>Fuel, staff time, late reports</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Nothing (it is a consumer)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>YES — monitoring / early-warning line</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NDMA ward officer / CBO — data + payer candidate</t>
+          <t>NGO / CBO project — BUYER (M&amp;E)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Ward ground truth on water and pasture</t>
+          <t>Reach, evidence for funders</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Thin, late ground truth</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
+          <t>Expensive last-mile data collection</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Distribution and field access</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>YES — per ward per month</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NGO / county / insurer — payer candidates</t>
+          <t>Insurer / research institute — buyer, later</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Reach, M&amp;E, underwriting data</t>
+          <t>Underwriting data; longitudinal herd data</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Expensive last-mile collection</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
+          <t>Sample surveys, scarce baselines</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Nothing</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Later — needs 6+ months of records</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Chief / ward admin — distribution</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Order, service, being seen to help</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Nothing</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Baraza announcement, signboard</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2571,16 +3129,16 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Interviews completed</t>
+          <t>Interviews completed (10 pastoralists + 5 informants)</t>
         </is>
       </c>
       <c r="B4">
-        <f>COUNTA('03_Interview_Log'!A2:A11)</f>
+        <f>COUNTA('03_Interview_Log'!A2:A16)</f>
         <v/>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -2592,11 +3150,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A specific costly decision described</t>
+          <t>A specific costly decision described (D1)</t>
         </is>
       </c>
       <c r="B5">
-        <f>'02_Hypotheses'!P2</f>
+        <f>'02_Hypotheses'!U2</f>
         <v/>
       </c>
       <c r="C5" t="inlineStr">
@@ -2613,11 +3171,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>The channel works unaided</t>
+          <t>He already reports, or agrees to (S1)</t>
         </is>
       </c>
       <c r="B6">
-        <f>'02_Hypotheses'!P6</f>
+        <f>'02_Hypotheses'!U13</f>
         <v/>
       </c>
       <c r="C6" t="inlineStr">
@@ -2627,112 +3185,112 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>hypothesis U1</t>
+          <t>hypothesis S1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A real past payment for info or vet care</t>
+          <t>One tap completed unaided or accepted (S2)</t>
         </is>
       </c>
       <c r="B7">
-        <f>'02_Hypotheses'!P13</f>
+        <f>'02_Hypotheses'!U14</f>
         <v/>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>&gt;=5</t>
+          <t>&gt;=6</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>hypothesis V1</t>
+          <t>hypothesis S2</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>The herder pays for anything monthly</t>
+          <t>His reports are good enough to sell (S3)</t>
         </is>
       </c>
       <c r="B8">
-        <f>'02_Hypotheses'!P14</f>
+        <f>'02_Hypotheses'!U15</f>
         <v/>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>&gt;=4</t>
+          <t>&gt;=6</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>hypothesis V2</t>
+          <t>hypothesis S3</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Commitments accepted (callback / intro / test)</t>
+          <t>A buyer with a real current spend (V1)</t>
         </is>
       </c>
       <c r="B9">
-        <f>COUNTIF('03_Interview_Log'!S2:U16,"Y")</f>
+        <f>'02_Hypotheses'!U17</f>
         <v/>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>&gt;=4</t>
+          <t>&gt;=1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Appendix L</t>
+          <t>hypothesis V1 - informant interviews</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Someone will carry distribution</t>
+          <t>A budget line, owner and cycle (V2)</t>
         </is>
       </c>
       <c r="B10">
-        <f>'02_Hypotheses'!P15</f>
+        <f>'02_Hypotheses'!U18</f>
         <v/>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>&gt;=3</t>
+          <t>&gt;=1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>hypothesis V3</t>
+          <t>hypothesis V2 - informant interviews</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>The household (not just the owner) benefits</t>
+          <t>Commitments accepted (callback / intro / test)</t>
         </is>
       </c>
       <c r="B11">
-        <f>'02_Hypotheses'!P17</f>
+        <f>COUNTIF('03_Interview_Log'!S2:U16,"Y")</f>
         <v/>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>&gt;=6</t>
+          <t>&gt;=4</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>hypothesis I1</t>
+          <t>Appendix M / section 4 close</t>
         </is>
       </c>
     </row>
@@ -2743,7 +3301,7 @@
         </is>
       </c>
       <c r="B13" s="4">
-        <f>IF(B4&lt;4,"NOT ENOUGH INTERVIEWS YET",IF(B5&lt;4,"REFRAME / STOP - fewer than 4 of 10 can describe a specific, costly decision",IF(AND(B5&gt;=6,B6&gt;=6,B7&gt;=5,B10&gt;=4),"GO - the problem, the channel, the payer signal and the commitments all clear the bar","PIVOT - the problem is there but the channel, payer or segment is wrong: re-read section 8")))</f>
+        <f>IF(B4&lt;10,"NOT ENOUGH INTERVIEWS YET",IF(B5&lt;4,"REFRAME / STOP - fewer than 4 of 10 can describe a specific, costly decision",IF(AND(B5&gt;=6,B6&gt;=6,B7&gt;=6,B9&gt;=1,B10&gt;=1,B11&gt;=4),"GO - the problem, the supply habit, the buyer and the commitments all clear the bar",IF(B9&lt;1,"NO BUYER YET - the service may be real, but no institution currently pays to collect this data: re-read section 8 before building more","PIVOT - the problem or the buyer is there but the supply or the segment is wrong: re-read section 8"))))</f>
         <v/>
       </c>
     </row>
